--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>zuzbQnCF</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,21 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -483,25 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
+          <t xml:space="preserve">petersen m 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>QTAUlvUP</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>GbeXvnR8</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -509,21 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>v9WoiHGP</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>O48oHrZ1</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -531,21 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t xml:space="preserve">sather a 
+  ger </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>2FREIeA6</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -553,21 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>dfO6OQtS</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -575,21 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">schwengers p 
-  ger </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t xml:space="preserve">aytekin d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>txZLBQVC</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>SxFxJ44k</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -597,21 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">schwengers p 
-  ger </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Q1njn0Vm</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>txZLBQVC</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -619,21 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
-  ger </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t xml:space="preserve">fritz m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -641,21 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">dankert b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>QTAUlvUP</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>lGJdeemM</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -663,21 +695,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">aytekin d 
   ger </t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -685,25 +717,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">willenborg f 
   ger </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>lxrr7DgN</t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -711,21 +743,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">fritz m 
   ger </t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>lGJdeemM</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>lONsG15D</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -733,21 +765,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">sather a 
-  ger </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t xml:space="preserve">fritz m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -755,21 +791,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">sather a 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -777,21 +813,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">hempel r 
   ger </t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
+          <t>pdPRS0me</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -799,21 +835,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">aarnink a 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>YmfcAeCo</t>
+          <t>SQrxFAMl</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -821,21 +857,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">jollenbeck m 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -843,21 +879,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">osmers h 
+          <t xml:space="preserve">schroder r 
   ger </t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>4bJLk19p</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -865,25 +901,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">alt p 
-  ger </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>UyNNTYWE</t>
-        </is>
-      </c>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>v12aAJdR</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -891,21 +923,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">exner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>lxrr7DgN</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OzPMRhK3</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -913,25 +949,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>QTAUlvUP</t>
-        </is>
-      </c>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>lGJdeemM</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -939,21 +971,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">sather a 
   ger </t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>lGJdeemM</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -961,21 +993,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">bacher m 
   ger </t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -983,21 +1015,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">exner f 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OzPMRhK3</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1005,21 +1037,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">aarnink a 
+          <t xml:space="preserve">braun r 
   ger </t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>YmfcAeCo</t>
+          <t>tO31cZrF</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1027,21 +1059,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1049,21 +1081,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">petersen m 
+          <t xml:space="preserve">haslberger w 
   ger </t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1071,21 +1103,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">gerach t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t xml:space="preserve">haslberger w 
+  ger </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>UyNNTYWE</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IgZoGKFn</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1093,21 +1129,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
+          <t xml:space="preserve">heft f 
   ger </t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>pAXo2Kvn</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1115,42 +1151,270 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">aytekin d 
   ger </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2BYSk4KO</t>
+          <t>t0ZPdkUl</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
+          <t>tvOIPExA</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kampka r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">braun r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kampka r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>xzRzG0VI</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heft f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">willenborg f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>W67CmLPh</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2BYSk4KO</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>M5BRZDsC</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,7 +479,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +487,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">petersen m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
+          <t xml:space="preserve">aytekin d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +509,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">willenborg f 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>v9WoiHGP</t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +535,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">sather a 
-  ger </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
+          <t xml:space="preserve">fritz m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>lONsG15D</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +557,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">fritz m 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>QevvB2nf</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +583,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +605,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Q1njn0Vm</t>
-        </is>
-      </c>
+          <t xml:space="preserve">hempel r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>pdPRS0me</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,25 +627,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>SQrxFAMl</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -669,25 +649,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>QTAUlvUP</t>
-        </is>
-      </c>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>lGJdeemM</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -695,21 +671,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
+          <t xml:space="preserve">schroder r 
   ger </t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>4bJLk19p</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -717,25 +693,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>QTAUlvUP</t>
-        </is>
-      </c>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -743,21 +715,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>lxrr7DgN</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -765,25 +741,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>QevvB2nf</t>
-        </is>
-      </c>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>lGJdeemM</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -791,21 +763,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">sather a 
   ger </t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -813,21 +785,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">hempel r 
+          <t xml:space="preserve">bacher m 
   ger </t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>pdPRS0me</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -835,21 +807,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SQrxFAMl</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -857,21 +829,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">braun r 
   ger </t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>tO31cZrF</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -879,21 +851,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -901,21 +873,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">haslberger w 
   ger </t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -923,25 +895,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">haslberger w 
   ger </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>lxrr7DgN</t>
+          <t>UyNNTYWE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -949,21 +921,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">heft f 
   ger </t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>lGJdeemM</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -971,21 +943,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">sather a 
-  ger </t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t xml:space="preserve">aytekin d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -993,21 +969,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">bacher m 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1015,21 +991,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">kampka r 
   ger </t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1051,7 +1027,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1059,21 +1035,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">jollenbeck m 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1081,21 +1057,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">kampka r 
   ger </t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1103,25 +1079,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
-  ger </t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>UyNNTYWE</t>
-        </is>
-      </c>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1143,7 +1115,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1151,25 +1123,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>t0ZPdkUl</t>
-        </is>
-      </c>
+          <t xml:space="preserve">willenborg f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1177,21 +1145,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>EDRZkDzS</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>fcxqFy2l</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1199,222 +1171,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2BYSk4KO</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
-        <is>
-          <t>AoL97rX8</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">braun r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>tO31cZrF</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">burda m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>EDRZkDzS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kampka r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AoL97rX8</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">petersen m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>xzRzG0VI</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">heft f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>8E8qmw3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">willenborg f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>txZLBQVC</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>W67CmLPh</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schlager d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>8E86CPuD</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schlager d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2BYSk4KO</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
         <is>
           <t>M5BRZDsC</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,7 +479,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,21 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>GbeXvnR8</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -509,25 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>QTAUlvUP</t>
+          <t>v9WoiHGP</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>O48oHrZ1</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -535,21 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t xml:space="preserve">sather a 
+  ger </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>2FREIeA6</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -557,25 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>QevvB2nf</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>dfO6OQtS</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -583,21 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t xml:space="preserve">aytekin d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>SxFxJ44k</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -605,21 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">hempel r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Q1njn0Vm</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>pdPRS0me</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -627,21 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t xml:space="preserve">fritz m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SQrxFAMl</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -649,21 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
-  ger </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>QTAUlvUP</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>lGJdeemM</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -671,21 +695,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
+          <t xml:space="preserve">aytekin d 
   ger </t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -693,21 +717,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t xml:space="preserve">willenborg f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>QTAUlvUP</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -715,25 +743,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
-  ger </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>lxrr7DgN</t>
-        </is>
-      </c>
+          <t xml:space="preserve">fritz m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>lONsG15D</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -741,21 +765,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t xml:space="preserve">fritz m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>lGJdeemM</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -763,21 +791,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">sather a 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -785,21 +813,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">bacher m 
+          <t xml:space="preserve">lechner f 
   ger </t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -807,21 +835,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">winter n 
   ger </t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -829,21 +857,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">braun r 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -851,21 +879,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">jollenbeck m 
+          <t xml:space="preserve">lechner f 
   ger </t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -873,21 +901,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -895,25 +923,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>UyNNTYWE</t>
+          <t>lxrr7DgN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -921,21 +949,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">heft f 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
+          <t>lGJdeemM</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -943,25 +971,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>t0ZPdkUl</t>
-        </is>
-      </c>
+          <t xml:space="preserve">sather a 
+  ger </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -969,21 +993,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">bacher m 
   ger </t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EDRZkDzS</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -991,21 +1015,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1013,21 +1037,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">braun r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t xml:space="preserve">winter n 
+  ger </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>trS1MB7T</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1035,21 +1063,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>EDRZkDzS</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1057,21 +1085,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">haslberger w 
   ger </t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1079,21 +1107,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">petersen m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t xml:space="preserve">haslberger w 
+  ger </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>UyNNTYWE</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1101,21 +1133,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">heft f 
+          <t xml:space="preserve">bauer t 
   ger </t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
+          <t>4fX0k7gg</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1123,21 +1155,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t xml:space="preserve">aytekin d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>pAXo2Kvn</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1145,42 +1181,218 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>txZLBQVC</t>
-        </is>
-      </c>
+          <t xml:space="preserve">bauer t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>4fX0k7gg</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kampka r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>xzRzG0VI</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heft f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">willenborg f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>2BYSk4KO</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>M5BRZDsC</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dankert b 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>rPfNaCdg</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>GzfvcwRj</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>CCww5Qfo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -513,18 +513,18 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>v9WoiHGP</t>
+          <t>lxrr7DgN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>
@@ -539,13 +539,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">sather a 
+          <t xml:space="preserve">bacher m 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
+          <t>lEwgk7go</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -565,18 +565,18 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">benen l 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
     </row>
@@ -591,18 +591,18 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
+          <t xml:space="preserve">heft f 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>0KMe4S4D</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Q1njn0Vm</t>
+          <t>AgnJojCs</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
+          <t xml:space="preserve">jablonski s 
   ger </t>
         </is>
       </c>
@@ -654,7 +654,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
     </row>
@@ -669,25 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">michel f 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>QTAUlvUP</t>
+          <t>02hM7hzd</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>lGJdeemM</t>
+          <t>4ljanukM</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -695,21 +695,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Wbz1kusU</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -717,25 +721,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>QTAUlvUP</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -743,21 +747,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -765,25 +773,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
+          <t xml:space="preserve">willenborg f 
   ger </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>SfKt2E6n</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -791,21 +799,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t xml:space="preserve">hempel r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -813,21 +825,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">lechner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -835,21 +851,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">winter n 
-  ger </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>txZLBQVC</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -857,21 +877,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
-  ger </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t xml:space="preserve">weisbach e 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>lli2SfLl</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -879,113 +903,97 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">lechner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dingert c 
-  ger </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>lxrr7DgN</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>IgZoGKFn</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welz t 
-  ger </t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>lGJdeemM</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sather a 
-  ger </t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>W67CmLPh</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -993,21 +1001,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">bacher m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>6u6i5pie</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1015,386 +1027,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>6q2yrHgU</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">winter n 
-  ger </t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>trS1MB7T</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>txZLBQVC</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>AiJ3kset</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jollenbeck m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YV3TqwPH</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">haslberger w 
-  ger </t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0AI1QUJH</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>l0ueP5rR</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">haslberger w 
-  ger </t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>UyNNTYWE</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0AI1QUJH</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>t2AoZLAa</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bauer t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>4fX0k7gg</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>jFMCm08e</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aytekin d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>zyLSrbZQ</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>xzRzG0VI</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>tvOIPExA</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bauer t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>4fX0k7gg</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kampka r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AoL97rX8</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hartmann r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>OzPMRhK3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">burda m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>EDRZkDzS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hartmann r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>OzPMRhK3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">petersen m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>xzRzG0VI</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">heft f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>8E8qmw3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">willenborg f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>txZLBQVC</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schlager d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2BYSk4KO</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dankert b 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>rPfNaCdg</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>GzfvcwRj</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
         </is>
       </c>
     </row>
@@ -487,18 +487,18 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">petersen m 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>CCww5Qfo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>
@@ -513,18 +513,18 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>v9WoiHGP</t>
+          <t>lxrr7DgN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>
@@ -539,13 +539,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">sather a 
+          <t xml:space="preserve">bacher m 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
+          <t>lEwgk7go</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -565,18 +565,18 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">benen l 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
     </row>
@@ -591,18 +591,18 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
+          <t xml:space="preserve">heft f 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>0KMe4S4D</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
     </row>
@@ -617,18 +617,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">exner f 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Q1njn0Vm</t>
+          <t>AgnJojCs</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
     </row>
@@ -643,18 +643,18 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
+          <t xml:space="preserve">jablonski s 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>rFNN7oyi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
     </row>
@@ -669,25 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">michel f 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>QTAUlvUP</t>
+          <t>02hM7hzd</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>lGJdeemM</t>
+          <t>4ljanukM</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -695,21 +695,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Wbz1kusU</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -717,25 +721,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>QTAUlvUP</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -743,21 +747,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -765,25 +773,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
+          <t xml:space="preserve">storks s 
   ger </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>SfKt2E6n</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -791,21 +799,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t xml:space="preserve">hempel r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -813,21 +825,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">lechner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>tnTvQd1l</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -835,21 +851,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">winter n 
-  ger </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>txZLBQVC</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -857,21 +877,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
-  ger </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t xml:space="preserve">weisbach e 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>lli2SfLl</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -879,21 +903,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">lechner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>W67CmLPh</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -901,21 +929,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>6u6i5pie</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -923,478 +955,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
-  ger </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>lxrr7DgN</t>
-        </is>
-      </c>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>8QPARz8c</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welz t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>lGJdeemM</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>hzyf0b9b</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sather a 
-  ger </t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>CpiTEcOi</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bacher m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>zyLSrbZQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>8CpxDyg4</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">siebert d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>MDhPV0RQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>6q2yrHgU</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">winter n 
-  ger </t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>trS1MB7T</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>txZLBQVC</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>AiJ3kset</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jollenbeck m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YV3TqwPH</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">haslberger w 
-  ger </t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0AI1QUJH</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>l0ueP5rR</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">haslberger w 
-  ger </t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>UyNNTYWE</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0AI1QUJH</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>t2AoZLAa</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bauer t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>4fX0k7gg</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>jFMCm08e</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aytekin d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>zyLSrbZQ</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>xzRzG0VI</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>tvOIPExA</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bauer t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>4fX0k7gg</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kampka r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AoL97rX8</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hartmann r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>OzPMRhK3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">burda m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>EDRZkDzS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hartmann r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>OzPMRhK3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">petersen m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>xzRzG0VI</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">heft f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>8E8qmw3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">willenborg f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>txZLBQVC</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schlager d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2BYSk4KO</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,54 +918,6 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>W67CmLPh</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stieler t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>pdPRS0me</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>6u6i5pie</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stieler t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zuzbQnCF</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
-  ger </t>
+          <t>CCww5Qfo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>rPfNaCdg</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>GbeXvnR8</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">osmers h 
-  ger </t>
+          <t>lxrr7DgN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CCww5Qfo</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>O48oHrZ1</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +496,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
-  ger </t>
+          <t>lEwgk7go</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lxrr7DgN</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>2FREIeA6</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +516,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">bacher m 
-  ger </t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lEwgk7go</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>dfO6OQtS</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +536,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">benen l 
-  ger </t>
+          <t>0KMe4S4D</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>QTAUlvUP</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>SxFxJ44k</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,330 +556,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">heft f 
-  ger </t>
+          <t>AgnJojCs</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0KMe4S4D</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>SxFxJ44k</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>AgnJojCs</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
           <t>UgdQz0fK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>t0w6KHuf</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jablonski s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>rFNN7oyi</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>AuVMGZvJ</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">michel f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>02hM7hzd</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>djSMofvg</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">siebert d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Wbz1kusU</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>U3QUqY85</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badstubner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>zyLSrbZQ</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>AgAeVYgC</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">petersen m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>SQrxFAMl</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>QVJwrCwI</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">storks s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SfKt2E6n</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>61DvZGfm</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hempel r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>0OYDmG9t</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">burda m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>tnTvQd1l</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>AVR8vwXP</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dingert c 
-  ger </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">weisbach e 
-  ger </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>lli2SfLl</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reichel t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>QevvB2nf</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,47 +453,49 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CCww5Qfo</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>rFNN7oyi</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>lxrr7DgN</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>02hM7hzd</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +503,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lEwgk7go</t>
+          <t xml:space="preserve">siebert d 
+  ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +529,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>QTAUlvUP</t>
+          <t xml:space="preserve">schroder r 
+  ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -536,19 +555,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0KMe4S4D</t>
+          <t xml:space="preserve">stieler t 
+  ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8f6APkLc</t>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -556,12 +581,148 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AgnJojCs</t>
+          <t xml:space="preserve">storks s 
+  ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>lli2SfLl</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,49 +453,59 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>rFNN7oyi</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>4ljanukM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schroder r 
+  ger </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>02hM7hzd</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -503,25 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -529,25 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -555,25 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -581,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">storks s 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -607,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">osmers h 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -633,25 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -659,68 +669,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">brand b 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stegemann s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>lli2SfLl</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welz t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>QevvB2nf</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
         <is>
           <t>GzfvcwRj</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,234 +453,360 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>QVJwrCwI</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>WzqXh8OL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zsmd0ggn</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">jablonski s 
   ger </t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>4ljanukM</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>U3QUqY85</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schroder r 
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UwsvBA74</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>pfoInmcq</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>AgAeVYgC</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stieler t 
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>QVJwrCwI</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>KUx4Q7x1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>K6A2elS9</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>61DvZGfm</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">osmers h 
-  ger </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>0OYDmG9t</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>AVR8vwXP</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brand b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stegemann s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welz t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,360 +453,52 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>QVJwrCwI</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>61DvZGfm</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>pdPRS0me</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>0OYDmG9t</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>AVR8vwXP</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>WzqXh8OL</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stegemann s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>f3ddUIXs</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>GzfvcwRj</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>zsmd0ggn</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jablonski s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>UwsvBA74</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jollenbeck m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vZqDdBhB</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brand b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>r7j4bXNb</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welz t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>WSMotj8U</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dankert b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>tI0qkTpo</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>x4pn9lxH</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">siebert d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
+          <t xml:space="preserve">petersen m 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>UwsvBA74</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,18 +487,200 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">gerach t 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CnrLfkNN</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8OhVCWxh</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -684,6 +684,240 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dCL13J5e</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pY1dP0SE</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zsmd0ggn</t>
+          <t>CnrLfkNN</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">petersen m 
-  ger </t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>UwsvBA74</t>
+          <t>8OhVCWxh</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,434 +476,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">gerach t 
-  ger </t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>vZqDdBhB</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">storks s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>r7j4bXNb</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jollenbeck m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WSMotj8U</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dankert b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tI0qkTpo</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badstubner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>x4pn9lxH</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dingert c 
-  ger </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>CnrLfkNN</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dankert b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>8OhVCWxh</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hartmann r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
           <t>IkCftsQm</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>dCL13J5e</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gerach t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>pY1dP0SE</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>QNoNA1DL</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dingert c 
-  ger </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>hvFA1cz8</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badstubner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>AeNg5uyq</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dingert c 
-  ger </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>IcrFCNr9</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">storks s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Uy2KjtMk</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>2k0SlKj2</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hartmann r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dQ0zIIKl</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jollenbeck m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>dCL13J5e</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t xml:space="preserve">brand b 
+  ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,12 +487,434 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IXf9Q08n</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>GzfvcwRj</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schroder r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6PecvuWE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>6PecvuWE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schroder r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>IXf9Q08n</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8nuIt455</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8nuIt455</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dCL13J5e</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">brand b 
-  ger </t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pY1dP0SE</t>
+          <t>QNoNA1DL</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">reichel t 
-  ger </t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QNoNA1DL</t>
+          <t>hvFA1cz8</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +496,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
-  ger </t>
+          <t>IXf9Q08n</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hvFA1cz8</t>
+          <t>AeNg5uyq</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +516,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
-  ger </t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IXf9Q08n</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AeNg5uyq</t>
+          <t>IcrFCNr9</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +536,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">reichel t 
-  ger </t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>IcrFCNr9</t>
+          <t>Uy2KjtMk</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +556,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">brych f 
-  ger </t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Uy2KjtMk</t>
+          <t>2k0SlKj2</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +576,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">osmers h 
-  ger </t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
+          <t>4ljanukM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2k0SlKj2</t>
+          <t>dQ0zIIKl</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,278 +596,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
-  ger </t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>dQ0zIIKl</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jablonski s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
           <t>6PecvuWE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>rsNyMnwK</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">siebert d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CIlrT3pm</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jablonski s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>6PecvuWE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6uSGCr06</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>f18BYPMP</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schroder r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Q5hiEzKD</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>IXf9Q08n</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SfGPAMUI</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brych f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>IukqGdk1</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schlager d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>8nuIt455</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>pWnjRsFa</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">osmers h 
-  ger </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>8nuIt455</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>bFO8E4Vg</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brand b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>rsNyMnwK</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t xml:space="preserve">petersen m 
+  ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>CIlrT3pm</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,12 +487,434 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UajsPCkT</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tbtaPLqC</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>GzfvcwRj</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,12 +459,7 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">petersen m 
-  ger </t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>GzfvcwRj</t>
@@ -485,12 +480,7 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jollenbeck m 
-  ger </t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>UgdQz0fK</t>
@@ -511,12 +501,7 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hartmann r 
-  ger </t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>4ljanukM</t>
@@ -537,12 +522,7 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brand b 
-  ger </t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>2VSFgl3c</t>
@@ -563,12 +543,7 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">storks s 
-  ger </t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>0jdIgO6t</t>
@@ -589,12 +564,7 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badstubner f 
-  ger </t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>hAcTWKKN</t>
@@ -615,12 +585,7 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stegemann s 
-  ger </t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>4fuCGs9P</t>
@@ -681,240 +646,6 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>K6A2elS9</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>UajsPCkT</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welz t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>tbtaPLqC</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">petersen m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ENOasf5c</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stegemann s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lpXDJjDj</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badstubner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dnhZQYKG</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brand b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zwD8uYZ9</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">storks s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>0KbQSfj4</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hartmann r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ShoJUGLi</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dankert b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>nc8W6DTp</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jollenbeck m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,197 +448,38 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rsNyMnwK</t>
+          <t>pWnjRsFa</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CIlrT3pm</t>
+          <t>bFO8E4Vg</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>6uSGCr06</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>f18BYPMP</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Q5hiEzKD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>SfGPAMUI</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>IukqGdk1</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>pWnjRsFa</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welz t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>bFO8E4Vg</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dankert b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>K6A2elS9</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,27 +453,28 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pWnjRsFa</t>
+          <t>UajsPCkT</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bFO8E4Vg</t>
+          <t>tbtaPLqC</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,12 +482,336 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t xml:space="preserve">stieler t 
+  ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UajsPCkT</t>
+          <t>0KbQSfj4</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -462,45 +462,40 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tbtaPLqC</t>
+          <t>ShoJUGLi</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stieler t 
-  ger </t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ENOasf5c</t>
+          <t>nc8W6DTp</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -509,82 +504,97 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lpXDJjDj</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8f6APkLc</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dnhZQYKG</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>4ljanukM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zwD8uYZ9</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -592,25 +602,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -618,25 +628,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -644,25 +654,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">reichel t 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -670,25 +680,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">gerach t 
+          <t xml:space="preserve">jablonski s 
   ger </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -696,25 +706,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">exner f 
+          <t xml:space="preserve">reichel t 
   ger </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -722,96 +732,18 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>M93rhBJF</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">siebert d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
           <t>YZPE6Sx7</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Eq0zfXl3</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brych f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>E7rNpTBk</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">siebert d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,70 +453,85 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>vZA6VYpf</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -524,25 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -550,25 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">exner f 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -576,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M93rhBJF</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -602,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">badstubner f 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Eq0zfXl3</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -628,25 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">reichel t 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>E7rNpTBk</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -654,25 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2mcmYkSq</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -680,25 +695,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">jablonski s 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -712,7 +727,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -724,7 +739,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>ELNeaSQr</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -738,12 +753,168 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>8f6APkLc</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -459,12 +459,7 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dingert c 
-  ger </t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>hpYJ6izc</t>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,28 +453,33 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -482,434 +487,18 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>r3GGwC4M</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brand b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>M93rhBJF</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badstubner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Eq0zfXl3</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">burda m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>E7rNpTBk</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stegemann s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>2mcmYkSq</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">osmers h 
-  ger </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>nBwH6AY8</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reichel t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>rPiijklS</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
           <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>8f6APkLc</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>YZPE6Sx7</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>4E8uaJWa</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badstubner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>x0haJmIE</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reichel t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ELNeaSQr</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welz t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Mku6FvHt</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">burda m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rwXP4l3L</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hartmann r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>MiACepQ7</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hartmann r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WQadeyWO</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brand b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ABBmcc1C</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brand b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>zyC4c6ee</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">osmers h 
-  ger </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">reichel t 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>4ljanukM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,18 +487,434 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ELNeaSQr</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>8f6APkLc</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>GnZmQeVb</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>raQ4MDUN</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,12 +459,7 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">siebert d 
-  ger </t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>vZA6VYpf</t>
@@ -485,12 +480,7 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jollenbeck m 
-  ger </t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>YZPE6Sx7</t>
@@ -511,12 +501,7 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dankert b 
-  ger </t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>vZA6VYpf</t>
@@ -537,12 +522,7 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schlager d 
-  ger </t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>IkCftsQm</t>
@@ -563,12 +543,7 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gerach t 
-  ger </t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>K6A2elS9</t>
@@ -589,64 +564,59 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">brych f 
   ger </t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>WQadeyWO</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stieler t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>ABBmcc1C</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brych f 
-  ger </t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>A15eUM4C</t>
@@ -681,240 +651,6 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>8f6APkLc</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IHYEDIog</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stieler t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>jVWMBdG5</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gerach t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>485V7EFU</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">storks s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8MVuSH0n</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jollenbeck m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2q7yHiho</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">siebert d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>AoSdOZaB</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dankert b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>dr2N9zoI</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>GnZmQeVb</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>raQ4MDUN</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schlager d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,133 +453,163 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4E8uaJWa</t>
+          <t>IHYEDIog</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>x0haJmIE</t>
+          <t>jVWMBdG5</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ELNeaSQr</t>
+          <t>485V7EFU</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Mku6FvHt</t>
+          <t>8MVuSH0n</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>rwXP4l3L</t>
+          <t>2q7yHiho</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MiACepQ7</t>
+          <t>AoSdOZaB</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WQadeyWO</t>
+          <t>dr2N9zoI</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -587,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">jablonski s 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ABBmcc1C</t>
+          <t>GnZmQeVb</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -613,25 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">brych f 
+          <t xml:space="preserve">petersen m 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zyC4c6ee</t>
+          <t>raQ4MDUN</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -639,18 +669,252 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">storks s 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>v3DAZKP9</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>biQrHC9r</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>nee3ysec</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6HTjFjve</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YmumZjET</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>j5mWxZE4</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>M5BRZDsC</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>UJQITUyi</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>UkaNveph</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xMovyDqH</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hartmann r 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>4bJLk19p</t>
         </is>
       </c>
     </row>
@@ -487,18 +487,18 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">osmers h 
+          <t xml:space="preserve">haslberger w 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8f6APkLc</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -539,18 +539,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">reichel t 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
     </row>
@@ -565,18 +565,18 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">kampka r 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>4fX0k7gg</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
+          <t>4ljanukM</t>
         </is>
       </c>
     </row>
@@ -591,18 +591,18 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">willenborg f 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>SMaB5LKo</t>
         </is>
       </c>
     </row>
@@ -617,18 +617,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">jablonski s 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
     </row>
@@ -643,18 +643,18 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">petersen m 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
     </row>
@@ -669,252 +669,18 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">badstubner f 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>v3DAZKP9</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jablonski s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>biQrHC9r</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badstubner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>nee3ysec</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welz t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>6HTjFjve</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YmumZjET</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hartmann r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
           <t>4fuCGs9P</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>j5mWxZE4</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">petersen m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>UJQITUyi</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dingert c 
-  ger </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>UkaNveph</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">osmers h 
-  ger </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xMovyDqH</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reichel t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IHYEDIog</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jVWMBdG5</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>485V7EFU</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">exner f 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8MVuSH0n</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,7 +539,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
@@ -550,14 +550,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2q7yHiho</t>
+          <t>YmumZjET</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,13 +565,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">willenborg f 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4fX0k7gg</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AoSdOZaB</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
+          <t xml:space="preserve">dankert b 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SMaB5LKo</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dr2N9zoI</t>
+          <t>UJQITUyi</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
@@ -635,7 +635,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>GnZmQeVb</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,25 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>UkPWzhq8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>raQ4MDUN</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -669,18 +669,18 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">brych f 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/germany/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,231 +456,363 @@
           <t>v3DAZKP9</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>biQrHC9r</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>nee3ysec</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>6HTjFjve</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>YmumZjET</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>j5mWxZE4</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>UJQITUyi</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>UkaNveph</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>UkPWzhq8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>xMovyDqH</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EuQnZBVQ</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2qNaDU87</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">willenborg f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pOGITkgl</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>vZA6VYpf</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>biQrHC9r</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">siebert d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>nee3ysec</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>E38ZP7hD</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>pfoInmcq</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>6HTjFjve</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>fwAoyY0E</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>UkPWzhq8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SrjMmBpK</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>hpYJ6izc</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>YmumZjET</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">willenborg f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>j5mWxZE4</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6w5RRTN0</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">dankert b 
   ger </t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>4fuCGs9P</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>UJQITUyi</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stegemann s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>UkaNveph</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schlager d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>UkPWzhq8</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>xMovyDqH</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brych f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>
